--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:21:18+00:00</t>
+    <t>2025-02-10T11:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2448" uniqueCount="386">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T11:27:45+00:00</t>
+    <t>2025-02-12T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,22 +502,6 @@
   </si>
   <si>
     <t>Anzahl der Tage, für welche kein Kostenbeitrag seitens der Krankenanstalt eingehoben wurde</t>
-  </si>
-  <si>
-    <t>Account.extension:ClaimRef</t>
-  </si>
-  <si>
-    <t>ClaimRef</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-ClaimRef}
-</t>
-  </si>
-  <si>
-    <t>Claim Referenz</t>
-  </si>
-  <si>
-    <t>Referenz vom Account auf den Claim.</t>
   </si>
   <si>
     <t>Account.modifierExtension</t>
@@ -1544,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL73"/>
+  <dimension ref="A1:AL72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.92578125" customWidth="true" bestFit="true"/>
@@ -2995,13 +2979,11 @@
         <v>156</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="C14" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>19</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3014,22 +2996,26 @@
         <v>19</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>19</v>
       </c>
@@ -3077,7 +3063,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -3095,19 +3081,19 @@
         <v>19</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>19</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3120,26 +3106,22 @@
         <v>19</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O15" t="s" s="2">
         <v>166</v>
       </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>19</v>
       </c>
@@ -3187,7 +3169,7 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3199,21 +3181,21 @@
         <v>19</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>129</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3221,22 +3203,22 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>170</v>
@@ -3244,7 +3226,9 @@
       <c r="M16" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="N16" s="2"/>
+      <c r="N16" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -3269,13 +3253,13 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>19</v>
+        <v>173</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>19</v>
+        <v>174</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -3293,13 +3277,13 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>19</v>
@@ -3308,18 +3292,18 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3327,7 +3311,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>84</v>
@@ -3336,23 +3320,21 @@
         <v>19</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>104</v>
+        <v>178</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>177</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -3377,13 +3359,13 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -3401,10 +3383,10 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>84</v>
@@ -3416,18 +3398,18 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>181</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3450,13 +3432,13 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3483,7 +3465,7 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Y18" t="s" s="2">
         <v>187</v>
@@ -3507,7 +3489,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3522,22 +3504,22 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>19</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3556,13 +3538,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3589,13 +3571,13 @@
         <v>19</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>193</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>19</v>
@@ -3613,7 +3595,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3628,29 +3610,29 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>19</v>
@@ -3662,15 +3644,17 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -3719,13 +3703,13 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>19</v>
@@ -3734,29 +3718,29 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>204</v>
+        <v>19</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>19</v>
@@ -3768,16 +3752,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3827,13 +3811,13 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>19</v>
@@ -3842,18 +3826,18 @@
         <v>96</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3864,7 +3848,7 @@
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>19</v>
@@ -3876,16 +3860,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3935,13 +3919,13 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>19</v>
@@ -3950,18 +3934,18 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3972,7 +3956,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>19</v>
@@ -3981,10 +3965,10 @@
         <v>19</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>220</v>
@@ -3992,9 +3976,7 @@
       <c r="M23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N23" t="s" s="2">
-        <v>222</v>
-      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>19</v>
@@ -4043,44 +4025,44 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>19</v>
@@ -4092,15 +4074,17 @@
         <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>19</v>
@@ -4149,37 +4133,37 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4192,10 +4176,10 @@
         <v>19</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
         <v>131</v>
@@ -4207,9 +4191,11 @@
         <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>19</v>
       </c>
@@ -4275,7 +4261,7 @@
         <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>229</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26">
@@ -4287,26 +4273,26 @@
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>235</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>236</v>
@@ -4314,12 +4300,8 @@
       <c r="M26" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="N26" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>19</v>
       </c>
@@ -4367,25 +4349,25 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>238</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>129</v>
       </c>
     </row>
     <row r="27">
@@ -4397,11 +4379,11 @@
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>84</v>
@@ -4416,15 +4398,17 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -4476,7 +4460,7 @@
         <v>239</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>84</v>
@@ -4491,19 +4475,19 @@
         <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>245</v>
+        <v>19</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4522,17 +4506,15 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N28" t="s" s="2">
         <v>249</v>
       </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -4581,7 +4563,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4724,7 +4706,7 @@
         <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>19</v>
@@ -4733,16 +4715,16 @@
         <v>19</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>259</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4799,7 +4781,7 @@
         <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>19</v>
@@ -4811,15 +4793,15 @@
         <v>19</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4830,7 +4812,7 @@
         <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>19</v>
@@ -4842,13 +4824,13 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>262</v>
+        <v>220</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
+        <v>221</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4899,44 +4881,44 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>264</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>19</v>
@@ -4948,15 +4930,17 @@
         <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>19</v>
@@ -5005,37 +4989,37 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5048,10 +5032,10 @@
         <v>19</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>131</v>
@@ -5063,9 +5047,11 @@
         <v>232</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>19</v>
       </c>
@@ -5131,51 +5117,47 @@
         <v>19</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>229</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>264</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>19</v>
       </c>
@@ -5223,25 +5205,25 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>129</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35">
@@ -5257,7 +5239,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>84</v>
@@ -5332,7 +5314,7 @@
         <v>268</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>84</v>
@@ -5378,13 +5360,13 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5453,15 +5435,15 @@
         <v>19</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5472,7 +5454,7 @@
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>19</v>
@@ -5481,16 +5463,16 @@
         <v>19</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5541,33 +5523,33 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>96</v>
+        <v>280</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>281</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5578,7 +5560,7 @@
         <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>19</v>
@@ -5587,16 +5569,16 @@
         <v>19</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>283</v>
+        <v>220</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5647,44 +5629,44 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>285</v>
+        <v>19</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>19</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>19</v>
@@ -5696,15 +5678,17 @@
         <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>19</v>
@@ -5753,37 +5737,37 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5796,10 +5780,10 @@
         <v>19</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>131</v>
@@ -5811,9 +5795,11 @@
         <v>232</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
       </c>
@@ -5879,51 +5865,47 @@
         <v>19</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>229</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>236</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>19</v>
       </c>
@@ -5971,41 +5953,41 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>84</v>
@@ -6017,10 +5999,10 @@
         <v>19</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>246</v>
+        <v>289</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>290</v>
@@ -6053,13 +6035,11 @@
         <v>19</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>19</v>
+        <v>292</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>19</v>
@@ -6077,16 +6057,16 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>96</v>
@@ -6100,18 +6080,18 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>84</v>
@@ -6123,16 +6103,16 @@
         <v>19</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6159,11 +6139,13 @@
         <v>19</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>297</v>
+        <v>19</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>19</v>
@@ -6181,16 +6163,16 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>96</v>
@@ -6204,10 +6186,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6218,7 +6200,7 @@
         <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>19</v>
@@ -6230,13 +6212,13 @@
         <v>19</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>300</v>
+        <v>178</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6263,13 +6245,13 @@
         <v>19</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>19</v>
+        <v>300</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>19</v>
+        <v>301</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>19</v>
+        <v>302</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>19</v>
@@ -6287,16 +6269,16 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>298</v>
+        <v>19</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>96</v>
@@ -6310,10 +6292,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6324,7 +6306,7 @@
         <v>75</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>19</v>
@@ -6336,13 +6318,13 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>183</v>
+        <v>269</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6369,13 +6351,13 @@
         <v>19</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>305</v>
+        <v>19</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>306</v>
+        <v>19</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>19</v>
@@ -6393,13 +6375,13 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>19</v>
@@ -6416,10 +6398,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6430,7 +6412,7 @@
         <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>19</v>
@@ -6442,13 +6424,13 @@
         <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>274</v>
+        <v>178</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6475,10 +6457,10 @@
         <v>19</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>19</v>
+        <v>309</v>
       </c>
       <c r="Z46" t="s" s="2">
         <v>19</v>
@@ -6499,13 +6481,13 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>19</v>
@@ -6522,10 +6504,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6545,16 +6527,16 @@
         <v>19</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6581,10 +6563,10 @@
         <v>19</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>314</v>
+        <v>19</v>
       </c>
       <c r="Z47" t="s" s="2">
         <v>19</v>
@@ -6605,7 +6587,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -6617,7 +6599,7 @@
         <v>19</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>96</v>
+        <v>313</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>19</v>
@@ -6628,10 +6610,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6642,7 +6624,7 @@
         <v>75</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>19</v>
@@ -6651,16 +6633,16 @@
         <v>19</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>316</v>
+        <v>220</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>317</v>
+        <v>221</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6711,44 +6693,44 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>318</v>
+        <v>19</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>19</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>19</v>
@@ -6760,15 +6742,17 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -6817,37 +6801,37 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6860,10 +6844,10 @@
         <v>19</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>131</v>
@@ -6875,9 +6859,11 @@
         <v>232</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
       </c>
@@ -6943,51 +6929,47 @@
         <v>19</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>229</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>131</v>
+        <v>241</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>236</v>
+        <v>318</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -7035,41 +7017,41 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>238</v>
+        <v>317</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>84</v>
@@ -7081,16 +7063,16 @@
         <v>19</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>246</v>
+        <v>321</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7117,13 +7099,11 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>19</v>
+        <v>324</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -7141,16 +7121,16 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>19</v>
+        <v>325</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>96</v>
@@ -7164,18 +7144,18 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>293</v>
+        <v>19</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>84</v>
@@ -7187,10 +7167,10 @@
         <v>19</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>326</v>
+        <v>295</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>327</v>
@@ -7223,11 +7203,13 @@
         <v>19</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>329</v>
+        <v>19</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>19</v>
@@ -7245,16 +7227,16 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI53" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>330</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>96</v>
@@ -7268,10 +7250,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7282,7 +7264,7 @@
         <v>75</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>19</v>
@@ -7294,13 +7276,13 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>300</v>
+        <v>178</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7327,10 +7309,10 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="Z54" t="s" s="2">
         <v>19</v>
@@ -7351,16 +7333,16 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>96</v>
@@ -7374,10 +7356,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7400,13 +7382,13 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7433,10 +7415,10 @@
         <v>19</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>19</v>
@@ -7457,7 +7439,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -7480,10 +7462,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7503,16 +7485,16 @@
         <v>19</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>183</v>
+        <v>336</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7539,10 +7521,10 @@
         <v>19</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>314</v>
+        <v>19</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>19</v>
@@ -7563,7 +7545,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7586,10 +7568,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7609,16 +7591,16 @@
         <v>19</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>343</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7669,7 +7651,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7692,10 +7674,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7706,7 +7688,7 @@
         <v>75</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>19</v>
@@ -7718,13 +7700,13 @@
         <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>345</v>
+        <v>220</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>346</v>
+        <v>221</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7775,44 +7757,44 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>344</v>
+        <v>222</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>19</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
@@ -7824,15 +7806,17 @@
         <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -7881,37 +7865,37 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -7924,10 +7908,10 @@
         <v>19</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
         <v>131</v>
@@ -7939,9 +7923,11 @@
         <v>232</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
       </c>
@@ -8007,51 +7993,47 @@
         <v>19</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>229</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>236</v>
+        <v>346</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>19</v>
       </c>
@@ -8075,13 +8057,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>19</v>
+        <v>181</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>19</v>
+        <v>348</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>19</v>
+        <v>349</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -8099,25 +8081,25 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>238</v>
+        <v>345</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -8133,7 +8115,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>84</v>
@@ -8148,13 +8130,13 @@
         <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>183</v>
+        <v>351</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8181,13 +8163,13 @@
         <v>19</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>354</v>
+        <v>19</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>19</v>
@@ -8208,7 +8190,7 @@
         <v>350</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>84</v>
@@ -8228,10 +8210,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8239,7 +8221,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>84</v>
@@ -8254,13 +8236,13 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8287,13 +8269,11 @@
         <v>19</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>19</v>
+        <v>357</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>19</v>
@@ -8311,10 +8291,10 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>84</v>
@@ -8334,10 +8314,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8348,7 +8328,7 @@
         <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -8360,13 +8340,13 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8393,11 +8373,13 @@
         <v>19</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>19</v>
@@ -8415,13 +8397,13 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>19</v>
@@ -8438,10 +8420,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8452,7 +8434,7 @@
         <v>75</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>19</v>
@@ -8464,13 +8446,13 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>364</v>
+        <v>220</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>365</v>
+        <v>221</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8521,44 +8503,44 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>363</v>
+        <v>222</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>19</v>
+        <v>223</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>19</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>19</v>
+        <v>157</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>19</v>
@@ -8570,15 +8552,17 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>198</v>
+        <v>131</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>19</v>
@@ -8627,37 +8611,37 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -8670,10 +8654,10 @@
         <v>19</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>131</v>
@@ -8685,9 +8669,11 @@
         <v>232</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
       </c>
@@ -8753,51 +8739,47 @@
         <v>19</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>229</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>235</v>
+        <v>19</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>236</v>
+        <v>365</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>19</v>
       </c>
@@ -8821,13 +8803,13 @@
         <v>19</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>19</v>
+        <v>367</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>19</v>
+        <v>368</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>19</v>
+        <v>369</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>19</v>
@@ -8845,33 +8827,33 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>238</v>
+        <v>364</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>129</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8894,13 +8876,13 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8927,14 +8909,14 @@
         <v>19</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="Z69" t="s" s="2">
-        <v>374</v>
-      </c>
       <c r="AA69" t="s" s="2">
         <v>19</v>
       </c>
@@ -8951,7 +8933,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -8974,10 +8956,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9000,13 +8982,13 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>183</v>
+        <v>269</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9033,13 +9015,13 @@
         <v>19</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>372</v>
+        <v>19</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>373</v>
+        <v>19</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>378</v>
+        <v>19</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>19</v>
@@ -9057,7 +9039,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9080,10 +9062,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9091,7 +9073,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>84</v>
@@ -9106,13 +9088,13 @@
         <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>274</v>
+        <v>378</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9163,10 +9145,10 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>84</v>
@@ -9186,10 +9168,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9197,7 +9179,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>84</v>
@@ -9212,15 +9194,17 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -9269,10 +9253,10 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="AH72" t="s" s="2">
         <v>84</v>
@@ -9287,114 +9271,6 @@
         <v>19</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AL73" t="s" s="2">
         <v>19</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:32:14+00:00</t>
+    <t>2025-02-12T10:54:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T10:54:19+00:00</t>
+    <t>2025-02-13T11:55:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T11:55:14+00:00</t>
+    <t>2025-02-13T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:01:49+00:00</t>
+    <t>2025-02-13T12:22:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:22:49+00:00</t>
+    <t>2025-02-13T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://example.org/StructureDefinition/MopedAccount</t>
+    <t>https://elga.moped.at/StructureDefinition/MopedAccount</t>
   </si>
   <si>
     <t>Version</t>
@@ -54,19 +54,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T12:31:02+00:00</t>
+    <t>2025-02-13T14:17:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Example Publisher</t>
+    <t>ELGA GmbH</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Example Publisher (http://example.org/example-publisher)</t>
+    <t>ELGA GmbH (https://elga.gv.at)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -452,7 +452,7 @@
     <t>AnzahlVerlegungen</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-AnzahlVerlegungen}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-AnzahlVerlegungen}
 </t>
   </si>
   <si>
@@ -465,7 +465,7 @@
     <t>AnzahlBeurlaubungen</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-AnzahlBeurlaubungen}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-AnzahlBeurlaubungen}
 </t>
   </si>
   <si>
@@ -478,7 +478,7 @@
     <t>WorkflowStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-workflow-status}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-workflow-status}
 </t>
   </si>
   <si>
@@ -494,7 +494,7 @@
     <t>TageOhneKostenbeitrag</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-TageOhneKostenbeitrag}
+    <t xml:space="preserve">Extension {https://elga.moped.at/StructureDefinition/moped-ext-TageOhneKostenbeitrag}
 </t>
   </si>
   <si>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:17:28+00:00</t>
+    <t>2025-02-13T14:29:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:29:22+00:00</t>
+    <t>2025-02-13T14:40:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:40:19+00:00</t>
+    <t>2025-02-13T14:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:46:33+00:00</t>
+    <t>2025-02-13T14:59:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T14:59:23+00:00</t>
+    <t>2025-02-14T09:24:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:24:21+00:00</t>
+    <t>2025-02-14T09:29:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:29:02+00:00</t>
+    <t>2025-02-14T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:34:15+00:00</t>
+    <t>2025-02-19T07:14:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T07:14:32+00:00</t>
+    <t>2025-02-19T08:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T08:04:21+00:00</t>
+    <t>2025-02-19T15:11:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:11:41+00:00</t>
+    <t>2025-02-19T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:18:38+00:00</t>
+    <t>2025-02-19T15:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T15:36:14+00:00</t>
+    <t>2025-02-20T20:13:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:13:59+00:00</t>
+    <t>2025-02-20T20:24:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T20:24:20+00:00</t>
+    <t>2025-02-27T10:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:01:21+00:00</t>
+    <t>2025-02-27T10:07:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T10:07:48+00:00</t>
+    <t>2025-03-01T14:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T14:53:36+00:00</t>
+    <t>2025-03-01T15:19:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-01T15:19:11+00:00</t>
+    <t>2025-03-02T20:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:51:11+00:00</t>
+    <t>2025-03-02T20:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T20:57:05+00:00</t>
+    <t>2025-03-11T16:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:13:30+00:00</t>
+    <t>2025-03-11T16:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T16:22:04+00:00</t>
+    <t>2025-03-12T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
+++ b/r5-ELGA-MOPED-Hackathon-2025/StructureDefinition-MopedAccount.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T12:46:26+00:00</t>
+    <t>2025-03-12T14:39:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
